--- a/ig/nr-INS-Patient/StructureDefinition-fr-core-organization-analysis-section.xlsx
+++ b/ig/nr-INS-Patient/StructureDefinition-fr-core-organization-analysis-section.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-16T12:02:48+00:00</t>
+    <t>2023-10-16T13:03:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
